--- a/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 10,27</t>
+          <t>-5,9; 10,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 13,26</t>
+          <t>-2,69; 13,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 6,43</t>
+          <t>-8,03; 6,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 9,76</t>
+          <t>-14,72; 10,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 171,8</t>
+          <t>-46,22; 193,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 259,05</t>
+          <t>-26,79; 258,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 131,41</t>
+          <t>-64,98; 118,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,52</t>
+          <t>-8,2; 6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 3,86</t>
+          <t>-11,19; 3,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 9,69</t>
+          <t>-5,35; 8,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 131,36</t>
+          <t>-62,16; 123,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 53,2</t>
+          <t>-70,76; 49,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 190,06</t>
+          <t>-45,51; 145,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 8,24</t>
+          <t>-5,8; 7,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 9,85</t>
+          <t>-4,75; 9,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 6,66</t>
+          <t>-12,54; 6,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 71,15</t>
+          <t>-6,9; 65,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 274,89</t>
+          <t>-64,55; 267,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 233,2</t>
+          <t>-47,35; 216,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 85,71</t>
+          <t>-70,87; 82,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,0</t>
+          <t>-4,92; 4,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,75</t>
+          <t>-5,06; 4,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,53</t>
+          <t>-6,3; 3,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 19,48</t>
+          <t>-1,2; 18,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 71,31</t>
+          <t>-43,15; 70,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 59,19</t>
+          <t>-41,41; 59,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 44,69</t>
+          <t>-49,34; 53,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 1614,84</t>
+          <t>-65,7; 2041,13</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 10,47</t>
+          <t>-2,58; 10,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 2,58</t>
+          <t>-8,86; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 9,97</t>
+          <t>1,03; 9,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 6,35</t>
+          <t>-10,15; 6,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 325,71</t>
+          <t>-37,33; 291,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 38,13</t>
+          <t>-60,77; 56,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 843,46</t>
+          <t>3,8; 755,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -0,16</t>
+          <t>-14,43; -0,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 8,06</t>
+          <t>-8,8; 8,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 19,72</t>
+          <t>-1,56; 18,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,84</t>
+          <t>0,0; 39,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,94; 19,42</t>
+          <t>-92,31; 20,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 134,17</t>
+          <t>-69,18; 151,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 457,43</t>
+          <t>-18,39; 492,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,83</t>
+          <t>-2,68; 2,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,56</t>
+          <t>-3,13; 2,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,88</t>
+          <t>-1,97; 3,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,07</t>
+          <t>-0,73; 9,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 39,67</t>
+          <t>-27,3; 38,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 29,48</t>
+          <t>-26,83; 27,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 55,19</t>
+          <t>-19,4; 50,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 425,89</t>
+          <t>-29,12; 401,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 10,26</t>
+          <t>-6,19; 9,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,56</t>
+          <t>-3,38; 13,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 6,09</t>
+          <t>-8,33; 6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 10,28</t>
+          <t>-14,29; 9,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 193,8</t>
+          <t>-47,28; 139,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 258,69</t>
+          <t>-28,57; 297,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 118,38</t>
+          <t>-66,8; 110,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 6,1</t>
+          <t>-7,89; 6,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 3,89</t>
+          <t>-11,22; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 8,61</t>
+          <t>-5,52; 9,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 123,36</t>
+          <t>-64,15; 126,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 49,33</t>
+          <t>-71,6; 56,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 145,63</t>
+          <t>-43,85; 155,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 7,77</t>
+          <t>-6,18; 8,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 9,79</t>
+          <t>-4,83; 10,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 6,98</t>
+          <t>-13,2; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 65,25</t>
+          <t>-6,66; 65,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 267,18</t>
+          <t>-71,15; 256,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 216,73</t>
+          <t>-43,32; 216,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 82,24</t>
+          <t>-71,02; 65,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,87</t>
+          <t>-4,01; 4,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 4,67</t>
+          <t>-4,92; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,83</t>
+          <t>-6,78; 3,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 18,84</t>
+          <t>-1,49; 17,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 70,17</t>
+          <t>-37,58; 78,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 59,36</t>
+          <t>-40,01; 67,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 53,51</t>
+          <t>-51,45; 43,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 2041,13</t>
+          <t>-59,08; 1470,35</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 10,0</t>
+          <t>-2,25; 10,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,86</t>
+          <t>-9,43; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,85</t>
+          <t>0,85; 9,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 6,14</t>
+          <t>-9,23; 6,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 291,73</t>
+          <t>-33,52; 325,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 56,86</t>
+          <t>-64,82; 37,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 755,09</t>
+          <t>2,65; 784,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -0,37</t>
+          <t>-14,74; -0,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 8,75</t>
+          <t>-9,11; 8,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 18,86</t>
+          <t>-1,72; 19,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,45</t>
+          <t>0,0; 38,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,31; 20,55</t>
+          <t>-91,63; 30,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 151,02</t>
+          <t>-68,52; 140,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 492,54</t>
+          <t>-19,61; 493,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,83</t>
+          <t>-2,38; 2,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,44</t>
+          <t>-2,88; 2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,64</t>
+          <t>-1,54; 3,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,08</t>
+          <t>-0,57; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 38,8</t>
+          <t>-24,92; 41,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 27,9</t>
+          <t>-25,62; 34,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 50,13</t>
+          <t>-16,56; 48,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 401,63</t>
+          <t>-17,54; 443,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-20,47%</t>
+          <t>-13,2%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 9,62</t>
+          <t>-4,9; 10,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 13,57</t>
+          <t>-2,82; 13,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 6,38</t>
+          <t>-7,73; 6,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 9,72</t>
+          <t>-14,99; 11,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 139,87</t>
+          <t>-43,37; 171,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 297,16</t>
+          <t>-29,0; 259,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 110,21</t>
+          <t>-66,8; 131,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 6,21</t>
+          <t>-8,29; 6,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 3,35</t>
+          <t>-11,56; 3,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 9,22</t>
+          <t>-5,03; 9,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 126,83</t>
+          <t>-61,61; 131,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,6; 56,54</t>
+          <t>-71,94; 53,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 155,64</t>
+          <t>-42,16; 190,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,06</t>
+          <t>20,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>582,06%</t>
+          <t>812,78%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 8,53</t>
+          <t>-5,55; 8,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 10,26</t>
+          <t>-4,27; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 5,45</t>
+          <t>-12,35; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 65,94</t>
+          <t>-5,02; 73,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 256,16</t>
+          <t>-70,68; 274,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 216,7</t>
+          <t>-40,73; 233,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 65,99</t>
+          <t>-68,22; 85,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>192,41%</t>
+          <t>228,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,83</t>
+          <t>-4,64; 5,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,29</t>
+          <t>-5,07; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 3,41</t>
+          <t>-6,3; 3,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 17,98</t>
+          <t>-1,24; 21,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,58; 78,04</t>
+          <t>-41,53; 71,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 67,83</t>
+          <t>-41,38; 59,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 43,69</t>
+          <t>-49,02; 44,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,08; 1470,35</t>
+          <t>-65,52; 1903,9</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,56%</t>
+          <t>-29,08%</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,75</t>
+          <t>-2,49; 10,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,26</t>
+          <t>-9,29; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,71</t>
+          <t>0,62; 9,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,51</t>
+          <t>-8,4; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 325,35</t>
+          <t>-31,7; 325,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 37,96</t>
+          <t>-63,5; 38,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 784,42</t>
+          <t>-15,24; 843,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -0,45</t>
+          <t>-14,78; -0,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 8,66</t>
+          <t>-9,65; 8,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 19,15</t>
+          <t>-0,9; 19,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>0,0; 36,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,63; 30,31</t>
+          <t>-91,94; 19,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,52; 140,87</t>
+          <t>-68,95; 134,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 493,23</t>
+          <t>-15,52; 457,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>101,82%</t>
+          <t>118,35%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,95</t>
+          <t>-2,28; 2,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,93</t>
+          <t>-2,89; 2,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,65</t>
+          <t>-1,53; 3,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 8,94</t>
+          <t>-0,53; 9,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 41,63</t>
+          <t>-22,75; 39,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 34,62</t>
+          <t>-26,23; 29,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 48,27</t>
+          <t>-15,47; 55,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 443,47</t>
+          <t>-28,73; 467,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-12,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-13,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.242495808111696</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.06096193863396</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.177578753404672</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.9692072223807302</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2344545424269442</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.5832906953106433</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1284286695140259</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1320241438231825</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,9; 10,27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,82; 13,26</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 6,43</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 11,81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 171,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-29,0; 259,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-66,8; 131,41</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.903625360169602</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.817612938000075</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.734458129902374</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-14.98591207322014</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4337129165676792</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2899867114585951</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6679930883653266</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.26915234633186</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13.25644132592634</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.426768537531484</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.81062300464101</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.717972920611472</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.590512147260076</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.314056152272119</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,38%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,29; 6,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-11,56; 3,86</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 9,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-61,61; 131,36</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-71,94; 53,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-42,16; 190,06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>-0.8368855205375753</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.016972435717116</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.913661810947803</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09145778434665862</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3338008076597391</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2057247552411296</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,86</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-24,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>812,78%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.2917299284289</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-11.55842940138866</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.03317764590427</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.6161021003736996</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7193682022507272</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4216451834441832</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,55; 8,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,27; 9,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-12,35; 6,66</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,02; 73,78</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-70,68; 274,89</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-40,73; 233,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-68,22; 85,71</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.516443423184327</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.859132478599861</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.694063937156137</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.313576509773894</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5319510847426974</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.900641420230548</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +805,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,34</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-13,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>228,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.6718225594630769</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.864489469047815</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.318565501493337</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>20.49058156119485</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.107245507066029</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3598595945961875</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2413188238670147</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>8.127843648030412</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 5,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 4,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 3,53</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 21,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,53; 71,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-41,38; 59,19</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-49,02; 44,69</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,52; 1903,9</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.546041732653535</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.272506461041422</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12.34800128143282</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.015676818409204</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7068440876610579</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4072976129396019</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6822201940200714</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.243870524433621</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.853326514849828</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.65783748464916</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>73.78141902484991</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.748912504258261</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.331950302530274</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.8570639089275641</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,86</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>59,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-26,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>170,27%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-29,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 10,47</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 2,58</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 9,97</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 5,14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-31,7; 325,71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-63,5; 38,13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-15,24; 843,46</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.06467982076241025</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05242122232168717</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.438869035082077</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7.341198735500273</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.007030576080330322</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.005137471016552404</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1398783865347724</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>2.286384536250464</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-7,35</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,22</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10,78</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-65,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-9,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.63829858866024</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.072151438125165</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.29765050597781</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.242038268860893</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4153378644132067</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4138092268132034</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4902462603566333</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.655240683684814</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-14,78; -0,16</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 8,06</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 19,72</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,41</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-91,94; 19,42</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-68,95; 134,17</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-15,52; 457,43</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.002258714719294</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.749400121479121</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.529766419786853</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>21.36737693614418</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7130886023746051</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5918946710234865</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4468662302242921</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>19.03898978379811</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1001,291 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-2,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>118,35%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.552038317449381</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.855252843219819</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4.698332446421276</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.231423546725925</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.5967840005966722</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2611099768653756</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1.702714097983516</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.290784762667705</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 2,83</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,89; 2,56</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 3,88</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 9,58</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-22,75; 39,67</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-26,23; 29,48</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-15,47; 55,19</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-28,73; 467,42</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.488017199597822</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.291672713116002</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.6204082696985103</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.396662659832664</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3169896784296451</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6350219507564513</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1523937950988886</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>10.46517663015274</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.577309718474993</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.97367675325321</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.135918546513325</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.257131865440118</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3812667679747524</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>8.434569745889794</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-7.352290239112652</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.9750805463323658</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>8.224686014973829</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>10.78161142948735</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.657155842415747</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.09511524056714318</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.006459952243284</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-14.78214584882809</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-9.651045037587762</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-0.9013785880961961</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.9193959574829794</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6894933697080106</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.1552160567110979</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-0.1613533023072943</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>8.05507891611966</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>19.7157762497209</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>36.40844579107654</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.194205132806532</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.341665321454426</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>4.574349055880448</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.1966491418197019</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.2097098130640324</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.045854712122669</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>3.947599339416016</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.02318199079149559</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.02072148966959142</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.1212364273367261</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>1.183458268947511</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.278930427475775</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.891877269162471</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.525970853106296</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.5295987657528611</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2275436850579243</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2622610818105573</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1547120321301641</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2872868873994805</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.828915138844808</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.558601442249603</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.879736490104242</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>9.575809894541569</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.3967217021277279</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.2948049298787409</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.5518842647705638</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>4.674200813837962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1293,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
